--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.17687816277839</v>
+        <v>8.478742701451488</v>
       </c>
       <c r="D2" t="n">
-        <v>52.06610385486609</v>
+        <v>8.46074187641574</v>
       </c>
       <c r="E2" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F2" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.15120279814676</v>
+        <v>3.762070454698848</v>
       </c>
       <c r="D3" t="n">
-        <v>23.16722421391432</v>
+        <v>3.764673934761077</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F3" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.8974033265648</v>
+        <v>4.69582804056678</v>
       </c>
       <c r="D4" t="n">
-        <v>25.24601178624282</v>
+        <v>4.102476915264458</v>
       </c>
       <c r="E4" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F4" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.67065713664286</v>
+        <v>6.283981784704465</v>
       </c>
       <c r="D5" t="n">
-        <v>41.05114744843974</v>
+        <v>6.670811460371457</v>
       </c>
       <c r="E5" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F5" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.03422128105142</v>
+        <v>5.693060958170856</v>
       </c>
       <c r="D6" t="n">
-        <v>34.80811035307262</v>
+        <v>5.656317932374301</v>
       </c>
       <c r="E6" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F6" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.24731550669802</v>
+        <v>4.102688769838427</v>
       </c>
       <c r="D7" t="n">
-        <v>12.49444320932754</v>
+        <v>2.030347021515726</v>
       </c>
       <c r="E7" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F7" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.03162748189533</v>
+        <v>6.667639465807992</v>
       </c>
       <c r="D8" t="n">
-        <v>40.90282652255241</v>
+        <v>6.646709309914767</v>
       </c>
       <c r="E8" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F8" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.37285444231505</v>
+        <v>7.373088846876196</v>
       </c>
       <c r="D9" t="n">
-        <v>45.76888394045466</v>
+        <v>7.437443640323883</v>
       </c>
       <c r="E9" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F9" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.0931630675789</v>
+        <v>8.302638998481571</v>
       </c>
       <c r="D10" t="n">
-        <v>51.03254207824043</v>
+        <v>8.29278808771407</v>
       </c>
       <c r="E10" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F10" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62.08164657130136</v>
+        <v>10.08826756783647</v>
       </c>
       <c r="D11" t="n">
-        <v>47.96207992895128</v>
+        <v>7.793837988454583</v>
       </c>
       <c r="E11" t="n">
-        <v>11.99717844476605</v>
+        <v>1.949541497274483</v>
       </c>
       <c r="F11" t="n">
-        <v>12.59129968536979</v>
+        <v>2.046086198872591</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
